--- a/セリフ編集/コーチ/コーチボイス.xlsx
+++ b/セリフ編集/コーチ/コーチボイス.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I300"/>
+  <dimension ref="A1:I348"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2127,7 +2127,7 @@
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.vague[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_roshi.strain_vague[1]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2142,19 +2142,19 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.vague[1]</t>
+          <t xml:space="preserve">sparta_roshi.strain_vague[1]</t>
         </is>
       </c>
       <c r="G70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目の色が変わってきた者が一人いる。名は伏せる</t>
+          <t xml:space="preserve">無理を通しとる奴がおる。誰とは言わん。……ああいうのは、後で来る</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.vague[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_roshi.strain_vague[2]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.vague[2]</t>
+          <t xml:space="preserve">sparta_roshi.strain_vague[2]</t>
         </is>
       </c>
       <c r="G71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習場の緊張は保たれている。緩みはない</t>
+          <t xml:space="preserve">ひとり、体に借りを作っとるな。今は保っとる。今はな</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.vague[3]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_roshi.strain_named[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2196,19 +2196,19 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.vague[3]</t>
+          <t xml:space="preserve">sparta_roshi.strain_named[1]</t>
         </is>
       </c>
       <c r="G72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足の運びが良くなった者がいる。誰かは言わない</t>
+          <t xml:space="preserve">{name}、よう追い込んどるが。……その無理が、いつか祟らんことをねがうばかりだ</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.named_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_roshi.strain_named[2]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2223,19 +2223,19 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.named_positive[1]</t>
+          <t xml:space="preserve">sparta_roshi.strain_named[2]</t>
         </is>
       </c>
       <c r="G73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、目の光が違う。悪くない</t>
+          <t xml:space="preserve">{name}の体は今、言うことを聞いとる。聞かんようになる日が来る</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.named_positive[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_roshi.strain_injured[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2250,19 +2250,19 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.named_positive[2]</t>
+          <t xml:space="preserve">sparta_roshi.strain_injured[1]</t>
         </is>
       </c>
       <c r="G74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}は今、波に乗っている。逃す手はない</t>
+          <t xml:space="preserve">{name}のあの怪我、大したことはない。……大したことにならんことを祈っとる</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.named_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_roshi.strain_injured[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2277,19 +2277,19 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.named_negative[1]</t>
+          <t xml:space="preserve">sparta_roshi.strain_injured[2]</t>
         </is>
       </c>
       <c r="G75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、足の踏ん張りが甘くなっている。何かある</t>
+          <t xml:space="preserve">{name}、軽い怪我だ。軽いうちは、な</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.named_negative[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.vague[1]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2304,19 +2304,19 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.named_negative[2]</t>
+          <t xml:space="preserve">sparta_tosho.vague[1]</t>
         </is>
       </c>
       <c r="G76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、目が泳いでいる。注意しておいた方がいい</t>
+          <t xml:space="preserve">目の色が変わってきた者が一人いる。名は伏せる</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.named_neutral[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.vague[2]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2331,19 +2331,19 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.named_neutral[1]</t>
+          <t xml:space="preserve">sparta_tosho.vague[2]</t>
         </is>
       </c>
       <c r="G77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}は変わらない。それも力のひとつ</t>
+          <t xml:space="preserve">練習場の緊張は保たれている。緩みはない</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.named_neutral[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.vague[3]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2358,19 +2358,19 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.named_neutral[2]</t>
+          <t xml:space="preserve">sparta_tosho.vague[3]</t>
         </is>
       </c>
       <c r="G78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、平熱を保っている。それでいい</t>
+          <t xml:space="preserve">足の運びが良くなった者がいる。誰かは言わない</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.stat_growing[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.named_positive[1]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.stat_growing[1]</t>
+          <t xml:space="preserve">sparta_tosho.named_positive[1]</t>
         </is>
       </c>
       <c r="G79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の{stat}、確かに上がっている。追い込んだ甲斐があった</t>
+          <t xml:space="preserve">{name}、目の光が違う。悪くない</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.stat_growing[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.named_positive[2]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2412,19 +2412,19 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.stat_growing[2]</t>
+          <t xml:space="preserve">sparta_tosho.named_positive[2]</t>
         </is>
       </c>
       <c r="G80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、{stat}が乗ってきている。ここが踏ん張り所</t>
+          <t xml:space="preserve">{name}は今、波に乗っている。逃す手はない</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.stat_stagnant[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.named_negative[1]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2439,19 +2439,19 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.stat_stagnant[1]</t>
+          <t xml:space="preserve">sparta_tosho.named_negative[1]</t>
         </is>
       </c>
       <c r="G81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の{stat}、壁にぶつかっている。ここからが本番</t>
+          <t xml:space="preserve">{name}、足の踏ん張りが甘くなっている。何かある</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.stat_stagnant[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.named_negative[2]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2466,19 +2466,19 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.stat_stagnant[2]</t>
+          <t xml:space="preserve">sparta_tosho.named_negative[2]</t>
         </is>
       </c>
       <c r="G82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、{stat}が止まった。甘えではない、壁</t>
+          <t xml:space="preserve">{name}、目が泳いでいる。注意しておいた方がいい</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.near_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.named_neutral[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2493,19 +2493,19 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.near_cap[1]</t>
+          <t xml:space="preserve">sparta_tosho.named_neutral[1]</t>
         </is>
       </c>
       <c r="G83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の{stat}、天井が見えている</t>
+          <t xml:space="preserve">{name}は変わらない。それも力のひとつ</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.near_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.named_neutral[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2520,19 +2520,19 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.near_cap[2]</t>
+          <t xml:space="preserve">sparta_tosho.named_neutral[2]</t>
         </is>
       </c>
       <c r="G84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、{stat}はもう伸びしろが乏しい。今の形を守るべき</t>
+          <t xml:space="preserve">{name}、平熱を保っている。それでいい</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.far_from_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.stat_growing[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2547,19 +2547,19 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.far_from_cap[1]</t>
+          <t xml:space="preserve">sparta_tosho.stat_growing[1]</t>
         </is>
       </c>
       <c r="G85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の{stat}、まだ底が見えない</t>
+          <t xml:space="preserve">{name}の{stat}、確かに上がっている。追い込んだ甲斐があった</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.far_from_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.stat_growing[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2574,19 +2574,19 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.far_from_cap[2]</t>
+          <t xml:space="preserve">sparta_tosho.stat_growing[2]</t>
         </is>
       </c>
       <c r="G86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、{stat}には余力がある。今が仕込み時</t>
+          <t xml:space="preserve">{name}、{stat}が乗ってきている。ここが踏ん張り所</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.vague[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2601,19 +2601,19 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.vague[1]</t>
+          <t xml:space="preserve">sparta_tosho.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="G87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全体のフォームのばらつきが、平均してやや小さくなっていますね</t>
+          <t xml:space="preserve">{name}の{stat}、壁にぶつかっている。ここからが本番</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.vague[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -2628,19 +2628,19 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.vague[2]</t>
+          <t xml:space="preserve">sparta_tosho.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="G88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習の集中度に、良い傾向が見えるデータがあります</t>
+          <t xml:space="preserve">{name}、{stat}が止まった。甘えではない、壁</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.vague[3]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.near_cap[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -2655,19 +2655,19 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.vague[3]</t>
+          <t xml:space="preserve">sparta_tosho.near_cap[1]</t>
         </is>
       </c>
       <c r="G89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一部の選手の反応速度に、伸びの兆候が出ています</t>
+          <t xml:space="preserve">{name}の{stat}、天井が見えている</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.named_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.near_cap[2]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -2682,19 +2682,19 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.named_positive[1]</t>
+          <t xml:space="preserve">sparta_tosho.near_cap[2]</t>
         </is>
       </c>
       <c r="G90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手、練習中の反応がここ数週で明らかに良くなっています</t>
+          <t xml:space="preserve">{name}、{stat}はもう伸びしろが乏しい。今の形を守るべき</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.named_positive[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.far_from_cap[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -2709,19 +2709,19 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.named_positive[2]</t>
+          <t xml:space="preserve">sparta_tosho.far_from_cap[1]</t>
         </is>
       </c>
       <c r="G91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手、集中の持続時間が延びている傾向が見て取れます</t>
+          <t xml:space="preserve">{name}の{stat}、まだ底が見えない</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.named_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.far_from_cap[2]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.named_negative[1]</t>
+          <t xml:space="preserve">sparta_tosho.far_from_cap[2]</t>
         </is>
       </c>
       <c r="G92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手、練習の集中指標がここ最近やや下がっています</t>
+          <t xml:space="preserve">{name}、{stat}には余力がある。今が仕込み時</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.named_negative[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.strain_vague[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -2763,19 +2763,19 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.named_negative[2]</t>
+          <t xml:space="preserve">sparta_tosho.strain_vague[1]</t>
         </is>
       </c>
       <c r="G93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手、動きの精度に小さなブレが増えてきています</t>
+          <t xml:space="preserve">無理を通している者がいる。名は伏せる。……ああいうのは、後から来る</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.named_neutral[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.strain_vague[2]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -2790,19 +2790,19 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.named_neutral[1]</t>
+          <t xml:space="preserve">sparta_tosho.strain_vague[2]</t>
         </is>
       </c>
       <c r="G94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手の各種指標は横ばい、安定していると言えますね</t>
+          <t xml:space="preserve">ひとり、体に借りを作っている。今は保っている。今は</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.named_neutral[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.strain_named[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -2817,19 +2817,19 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.named_neutral[2]</t>
+          <t xml:space="preserve">sparta_tosho.strain_named[1]</t>
         </is>
       </c>
       <c r="G95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手、特筆すべき変化は観測されていません</t>
+          <t xml:space="preserve">{name}、よく追い込んでいる。……その借り、いつか返すことになる</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.stat_growing[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.strain_named[2]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -2844,19 +2844,19 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.stat_growing[1]</t>
+          <t xml:space="preserve">sparta_tosho.strain_named[2]</t>
         </is>
       </c>
       <c r="G96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手の{stat}、数値上も明確な上昇曲線を描いています</t>
+          <t xml:space="preserve">{name}の体は今、言うことを聞いている。聞かなくなる日が来る</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.stat_growing[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.strain_injured[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -2871,19 +2871,19 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.stat_growing[2]</t>
+          <t xml:space="preserve">sparta_tosho.strain_injured[1]</t>
         </is>
       </c>
       <c r="G97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手の{stat}、直近の測定でも伸びが継続しています</t>
+          <t xml:space="preserve">{name}のあの怪我、大したことはない。……大したことにならないことを祈る</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.stat_stagnant[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.sparta_tosho.strain_injured[2]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -2898,19 +2898,19 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.stat_stagnant[1]</t>
+          <t xml:space="preserve">sparta_tosho.strain_injured[2]</t>
         </is>
       </c>
       <c r="G98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手の{stat}、ここ最近は数値が横ばいで、伸びが鈍化しています</t>
+          <t xml:space="preserve">{name}、軽い怪我だ。軽いうちは</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.stat_stagnant[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.vague[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -2925,19 +2925,19 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.stat_stagnant[2]</t>
+          <t xml:space="preserve">theorist.vague[1]</t>
         </is>
       </c>
       <c r="G99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手の{stat}、成長曲線が一時的にプラトーに入っているようです</t>
+          <t xml:space="preserve">全体のフォームのばらつきが、平均してやや小さくなっていますね</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.near_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.vague[2]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -2952,19 +2952,19 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.near_cap[1]</t>
+          <t xml:space="preserve">theorist.vague[2]</t>
         </is>
       </c>
       <c r="G100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手の{stat}、成長曲線の傾きから見て、上限にかなり近い水準です</t>
+          <t xml:space="preserve">練習の集中度に、良い傾向が見えるデータがあります</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.near_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.vague[3]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -2979,19 +2979,19 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.near_cap[2]</t>
+          <t xml:space="preserve">theorist.vague[3]</t>
         </is>
       </c>
       <c r="G101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手の{stat}、これ以上の伸びは統計的にも限定的だと見込まれます</t>
+          <t xml:space="preserve">一部の選手の反応速度に、伸びの兆候が出ています</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.far_from_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.named_positive[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3006,19 +3006,19 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.far_from_cap[1]</t>
+          <t xml:space="preserve">theorist.named_positive[1]</t>
         </is>
       </c>
       <c r="G102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手の{stat}、成長曲線を見る限り、まだ十分な伸び代が残っています</t>
+          <t xml:space="preserve">{name}選手、練習中の反応がここ数週で明らかに良くなっています</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.far_from_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.named_positive[2]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3033,19 +3033,19 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.far_from_cap[2]</t>
+          <t xml:space="preserve">theorist.named_positive[2]</t>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}選手の{stat}、上限との差はまだ大きく、投資に見合う数値です</t>
+          <t xml:space="preserve">{name}選手、集中の持続時間が延びている傾向が見て取れます</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.vague[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.named_negative[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3060,19 +3060,19 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.vague[1]</t>
+          <t xml:space="preserve">theorist.named_negative[1]</t>
         </is>
       </c>
       <c r="G104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……誰かの目つきが、変わった</t>
+          <t xml:space="preserve">{name}選手、練習の集中指標がここ最近やや下がっています</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.vague[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.named_negative[2]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3087,19 +3087,19 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.vague[2]</t>
+          <t xml:space="preserve">theorist.named_negative[2]</t>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……音が、いい。誰の足音かは言わん</t>
+          <t xml:space="preserve">{name}選手、動きの精度に小さなブレが増えてきています</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.vague[3]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.named_neutral[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3114,19 +3114,19 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.vague[3]</t>
+          <t xml:space="preserve">theorist.named_neutral[1]</t>
         </is>
       </c>
       <c r="G106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……たるんどる奴は、今はいない</t>
+          <t xml:space="preserve">{name}選手の各種指標は横ばい、安定していると言えますね</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.named_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.named_neutral[2]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3141,19 +3141,19 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.named_positive[1]</t>
+          <t xml:space="preserve">theorist.named_neutral[2]</t>
         </is>
       </c>
       <c r="G107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}、いい顔しとる</t>
+          <t xml:space="preserve">{name}選手、特筆すべき変化は観測されていません</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.named_positive[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.stat_growing[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3168,19 +3168,19 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.named_positive[2]</t>
+          <t xml:space="preserve">theorist.stat_growing[1]</t>
         </is>
       </c>
       <c r="G108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}、今は乗っとるな</t>
+          <t xml:space="preserve">{name}選手の{stat}、数値上も明確な上昇曲線を描いています</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.named_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.stat_growing[2]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3195,19 +3195,19 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.named_negative[1]</t>
+          <t xml:space="preserve">theorist.stat_growing[2]</t>
         </is>
       </c>
       <c r="G109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}、少し落ちとる</t>
+          <t xml:space="preserve">{name}選手の{stat}、直近の測定でも伸びが継続しています</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.named_negative[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3222,19 +3222,19 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.named_negative[2]</t>
+          <t xml:space="preserve">theorist.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="G110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}、何かある目だ</t>
+          <t xml:space="preserve">{name}選手の{stat}、ここ最近は数値が横ばいで、伸びが鈍化しています</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.named_neutral[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3249,19 +3249,19 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.named_neutral[1]</t>
+          <t xml:space="preserve">theorist.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="G111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}、いつも通りだ</t>
+          <t xml:space="preserve">{name}選手の{stat}、成長曲線が一時的にプラトーに入っているようです</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.named_neutral[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.near_cap[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3276,19 +3276,19 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.named_neutral[2]</t>
+          <t xml:space="preserve">theorist.near_cap[1]</t>
         </is>
       </c>
       <c r="G112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}、変わらん。それでいい</t>
+          <t xml:space="preserve">{name}選手の{stat}、成長曲線の傾きから見て、上限にかなり近い水準です</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.stat_growing[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.near_cap[2]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3303,19 +3303,19 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.stat_growing[1]</t>
+          <t xml:space="preserve">theorist.near_cap[2]</t>
         </is>
       </c>
       <c r="G113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}の{stat}、上がっとる。地味だが、確かだ</t>
+          <t xml:space="preserve">{name}選手の{stat}、これ以上の伸びは統計的にも限定的だと見込まれます</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.stat_growing[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.far_from_cap[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3330,19 +3330,19 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.stat_growing[2]</t>
+          <t xml:space="preserve">theorist.far_from_cap[1]</t>
         </is>
       </c>
       <c r="G114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}、{stat}に手応えがある</t>
+          <t xml:space="preserve">{name}選手の{stat}、成長曲線を見る限り、まだ十分な伸び代が残っています</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.stat_stagnant[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.far_from_cap[2]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3357,19 +3357,19 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.stat_stagnant[1]</t>
+          <t xml:space="preserve">theorist.far_from_cap[2]</t>
         </is>
       </c>
       <c r="G115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}の{stat}、止まっとる。焦る段階じゃない</t>
+          <t xml:space="preserve">{name}選手の{stat}、上限との差はまだ大きく、投資に見合う数値です</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.stat_stagnant[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.strain_vague[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3384,19 +3384,19 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.stat_stagnant[2]</t>
+          <t xml:space="preserve">theorist.strain_vague[1]</t>
         </is>
       </c>
       <c r="G116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}、{stat}が頭打ちだ。時間がかかる</t>
+          <t xml:space="preserve">練習負荷の累積が高い水準の選手がいます。今すぐどうという話ではありませんが</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.near_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.strain_vague[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -3411,19 +3411,19 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.near_cap[1]</t>
+          <t xml:space="preserve">theorist.strain_vague[2]</t>
         </is>
       </c>
       <c r="G117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}の{stat}、もう天井が近い</t>
+          <t xml:space="preserve">一部の選手で、負荷の累積が観測範囲の上の方に来ています。記録には残しておきます</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.near_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.strain_named[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -3438,19 +3438,19 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.near_cap[2]</t>
+          <t xml:space="preserve">theorist.strain_named[1]</t>
         </is>
       </c>
       <c r="G118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}、{stat}は伸びしろが少ない。守りに入る頃合いだ</t>
+          <t xml:space="preserve">{name}選手、負荷の累積が高い水準です。今の数値には出ていません。ただ、将来どうなる影響が出るかはわかりませんね</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.far_from_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.strain_named[2]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -3465,19 +3465,19 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.far_from_cap[1]</t>
+          <t xml:space="preserve">theorist.strain_named[2]</t>
         </is>
       </c>
       <c r="G119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}の{stat}、まだ奥がある</t>
+          <t xml:space="preserve">{name}選手、体は今のところ持ちこたえています。この種のものは遅れて現れるものですが</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.far_from_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.strain_injured[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -3492,19 +3492,19 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.far_from_cap[2]</t>
+          <t xml:space="preserve">theorist.strain_injured[1]</t>
         </is>
       </c>
       <c r="G120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}、{stat}はまだ伸びる。今は仕込み時だ</t>
+          <t xml:space="preserve">{name}選手の今回の負傷、軽微です。ただ、この種のものは記録に残り続けます</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.vague[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.theorist.strain_injured[2]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -3519,19 +3519,19 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.vague[1]</t>
+          <t xml:space="preserve">theorist.strain_injured[2]</t>
         </is>
       </c>
       <c r="G121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……どなたかの目つきが、変わりました</t>
+          <t xml:space="preserve">{name}選手、離脱は短期で済みます。累積としては一件、加算されますが</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.vague[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.vague[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -3546,19 +3546,19 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.vague[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.vague[1]</t>
         </is>
       </c>
       <c r="G122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足音が、良いのです。誰かは申しません</t>
+          <t xml:space="preserve">……誰かの目つきが、変わった</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.vague[3]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.vague[2]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -3573,19 +3573,19 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.vague[3]</t>
+          <t xml:space="preserve">artisan_bukotsu.vague[2]</t>
         </is>
       </c>
       <c r="G123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……たるんでいる方は、今はいませんよ</t>
+          <t xml:space="preserve">……音が、いい。誰の足音かは言わん</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.named_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.vague[3]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -3600,19 +3600,19 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.named_positive[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.vague[3]</t>
         </is>
       </c>
       <c r="G124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さん、いい顔をされています</t>
+          <t xml:space="preserve">……たるんどる奴は、今はいない</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.named_positive[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.named_positive[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -3627,19 +3627,19 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.named_positive[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.named_positive[1]</t>
         </is>
       </c>
       <c r="G125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さん、今は乗っていますね</t>
+          <t xml:space="preserve">……{name}、いい顔しとる</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.named_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.named_positive[2]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -3654,19 +3654,19 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.named_negative[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.named_positive[2]</t>
         </is>
       </c>
       <c r="G126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さん、少し落ちていますね</t>
+          <t xml:space="preserve">……{name}、今は乗っとるな</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.named_negative[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.named_negative[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -3681,19 +3681,19 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.named_negative[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.named_negative[1]</t>
         </is>
       </c>
       <c r="G127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さん、何かある目をされています</t>
+          <t xml:space="preserve">……{name}、少し落ちとる</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.named_neutral[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.named_negative[2]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -3708,19 +3708,19 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.named_neutral[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.named_negative[2]</t>
         </is>
       </c>
       <c r="G128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さん、いつも通りです</t>
+          <t xml:space="preserve">……{name}、何かある目だ</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.named_neutral[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.named_neutral[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -3735,19 +3735,19 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.named_neutral[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.named_neutral[1]</t>
         </is>
       </c>
       <c r="G129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さん、変わりません。それでいいのです</t>
+          <t xml:space="preserve">……{name}、いつも通りだ</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.stat_growing[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.named_neutral[2]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -3762,19 +3762,19 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.stat_growing[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.named_neutral[2]</t>
         </is>
       </c>
       <c r="G130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さんの{stat}、上がっています。地味ですが、確かです</t>
+          <t xml:space="preserve">……{name}、変わらん。それでいい</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.stat_growing[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.stat_growing[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -3789,19 +3789,19 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.stat_growing[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.stat_growing[1]</t>
         </is>
       </c>
       <c r="G131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さん、{stat}に手応えがあります</t>
+          <t xml:space="preserve">……{name}の{stat}、上がっとる。地味だが、確かだ</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.stat_stagnant[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.stat_growing[2]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -3816,19 +3816,19 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.stat_stagnant[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.stat_growing[2]</t>
         </is>
       </c>
       <c r="G132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さんの{stat}、止まっています。焦る段階ではありません</t>
+          <t xml:space="preserve">……{name}、{stat}に手応えがある</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.stat_stagnant[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -3843,19 +3843,19 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.stat_stagnant[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="G133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さん、{stat}が頭打ちです。時間がかかりますね</t>
+          <t xml:space="preserve">……{name}の{stat}、止まっとる。焦る段階じゃない</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.near_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -3870,19 +3870,19 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.near_cap[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="G134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さんの{stat}、もう天井が近いです</t>
+          <t xml:space="preserve">……{name}、{stat}が頭打ちだ。時間がかかる</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.near_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.near_cap[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -3897,19 +3897,19 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.near_cap[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.near_cap[1]</t>
         </is>
       </c>
       <c r="G135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さん、{stat}は伸びしろが少ないです。守りに入る頃合いですね</t>
+          <t xml:space="preserve">……{name}の{stat}、もう天井が近い</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.far_from_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.near_cap[2]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -3924,19 +3924,19 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.far_from_cap[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.near_cap[2]</t>
         </is>
       </c>
       <c r="G136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さんの{stat}、まだ奥があります</t>
+          <t xml:space="preserve">……{name}、{stat}は伸びしろが少ない。守りに入る頃合いだ</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.far_from_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.far_from_cap[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -3951,19 +3951,19 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.far_from_cap[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.far_from_cap[1]</t>
         </is>
       </c>
       <c r="G137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……{name}さん、{stat}はまだ伸びます。今は仕込み時ですね</t>
+          <t xml:space="preserve">……{name}の{stat}、まだ奥がある</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.vague[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.far_from_cap[2]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -3978,19 +3978,19 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.vague[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.far_from_cap[2]</t>
         </is>
       </c>
       <c r="G138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰かの表情が、最近柔らかくなってきましたよ</t>
+          <t xml:space="preserve">……{name}、{stat}はまだ伸びる。今は仕込み時だ</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.vague[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.strain_vague[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4005,19 +4005,19 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.vague[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.strain_vague[1]</t>
         </is>
       </c>
       <c r="G139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子かな……まだ誰とは言えませんが、いい変化があります</t>
+          <t xml:space="preserve">……ひとり、体を削っとる。誰とは言わん</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.vague[3]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.strain_vague[2]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4032,19 +4032,19 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.vague[3]</t>
+          <t xml:space="preserve">artisan_bukotsu.strain_vague[2]</t>
         </is>
       </c>
       <c r="G140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習場全体の空気が、少し温かくなった気がします</t>
+          <t xml:space="preserve">……無理を通しとる奴がおる。今は、保つ</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.named_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.strain_named[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4059,19 +4059,19 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.named_positive[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.strain_named[1]</t>
         </is>
       </c>
       <c r="G141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さん、最近すごく前向きな顔をしていますよ</t>
+          <t xml:space="preserve">……{name}、無理を通しとるな。……今は、な</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.named_positive[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.strain_named[2]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4086,19 +4086,19 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.named_positive[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.strain_named[2]</t>
         </is>
       </c>
       <c r="G142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さん、自分でも手応えを感じ始めているみたいです</t>
+          <t xml:space="preserve">……{name}、体に借りを作っとる。返す日が来る</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.named_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.strain_injured[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4113,19 +4113,19 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.named_negative[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.strain_injured[1]</t>
         </is>
       </c>
       <c r="G143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さん、少し元気がないかもしれません。気にかけてあげてください</t>
+          <t xml:space="preserve">……{name}のあれ、軽い怪我だが……。まぁ、軽いうちは、大丈夫だろう</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.named_negative[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_bukotsu.strain_injured[2]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4140,19 +4140,19 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.named_negative[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.strain_injured[2]</t>
         </is>
       </c>
       <c r="G144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さん、練習中に何か考え込んでいる時間が増えました</t>
+          <t xml:space="preserve">……{name}、すぐ戻る。だが、残る</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.named_neutral[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.vague[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4167,19 +4167,19 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.named_neutral[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.vague[1]</t>
         </is>
       </c>
       <c r="G145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さん、いつものペースでやっていますよ</t>
+          <t xml:space="preserve">……どなたかの目つきが、変わりました</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.named_neutral[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.vague[2]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4194,19 +4194,19 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.named_neutral[2]</t>
+          <t xml:space="preserve">artisan_seihitsu.vague[2]</t>
         </is>
       </c>
       <c r="G146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さん、落ち着いて過ごせているみたいです</t>
+          <t xml:space="preserve">……足音が、良いのです。誰かは申しません</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.stat_growing[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.vague[3]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4221,19 +4221,19 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.stat_growing[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.vague[3]</t>
         </is>
       </c>
       <c r="G147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さんの{stat}、着実に伸びてきていますよ。本人も気づいているはずです</t>
+          <t xml:space="preserve">……たるんでいる方は、今はいませんよ</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.stat_growing[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.named_positive[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4248,19 +4248,19 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.stat_growing[2]</t>
+          <t xml:space="preserve">artisan_seihitsu.named_positive[1]</t>
         </is>
       </c>
       <c r="G148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さん、{stat}が良くなってきています。焦らず続けましょう</t>
+          <t xml:space="preserve">……{name}さん、いい顔をされています</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.stat_stagnant[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.named_positive[2]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4275,19 +4275,19 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.stat_stagnant[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.named_positive[2]</t>
         </is>
       </c>
       <c r="G149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さんの{stat}、少し足踏みしていますね。でも悪いことではありませんよ</t>
+          <t xml:space="preserve">……{name}さん、今は乗っていますね</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.stat_stagnant[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.named_negative[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -4302,19 +4302,19 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.stat_stagnant[2]</t>
+          <t xml:space="preserve">artisan_seihitsu.named_negative[1]</t>
         </is>
       </c>
       <c r="G150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さん、{stat}が伸び悩んでいます。本人も気づいているみたいです</t>
+          <t xml:space="preserve">……{name}さん、少し落ちていますね</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.near_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.named_negative[2]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -4329,19 +4329,19 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.near_cap[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.named_negative[2]</t>
         </is>
       </c>
       <c r="G151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さんの{stat}、もう十分に高いところまで来ていますよ</t>
+          <t xml:space="preserve">……{name}さん、何かある目をされています</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.near_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.named_neutral[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -4356,19 +4356,19 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.near_cap[2]</t>
+          <t xml:space="preserve">artisan_seihitsu.named_neutral[1]</t>
         </is>
       </c>
       <c r="G152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さん、{stat}はこの先はゆっくりになると思います。それも成熟の証です</t>
+          <t xml:space="preserve">……{name}さん、いつも通りです</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.far_from_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.named_neutral[2]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -4383,19 +4383,19 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.far_from_cap[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.named_neutral[2]</t>
         </is>
       </c>
       <c r="G153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さんの{stat}、まだまだこれからですよ。楽しみです</t>
+          <t xml:space="preserve">……{name}さん、変わりません。それでいいのです</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.far_from_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.stat_growing[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -4410,19 +4410,19 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.far_from_cap[2]</t>
+          <t xml:space="preserve">artisan_seihitsu.stat_growing[1]</t>
         </is>
       </c>
       <c r="G154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}さん、{stat}には十分な余地が残っています。焦らず育てましょう</t>
+          <t xml:space="preserve">……{name}さんの{stat}、上がっています。地味ですが、確かです</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.vague[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.stat_growing[2]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -4437,19 +4437,19 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.vague[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.stat_growing[2]</t>
         </is>
       </c>
       <c r="G155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰とは言わないけどよ、目つきが変わった奴がいるんだよ</t>
+          <t xml:space="preserve">……{name}さん、{stat}に手応えがあります</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.vague[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -4464,19 +4464,19 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.vague[2]</t>
+          <t xml:space="preserve">artisan_seihitsu.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="G156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんかいい空気なんだよなあ、最近の練習場</t>
+          <t xml:space="preserve">……{name}さんの{stat}、止まっています。焦る段階ではありません</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.vague[3]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -4491,19 +4491,19 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.vague[3]</t>
+          <t xml:space="preserve">artisan_seihitsu.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="G157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">飯の食い方見てりゃわかるもんさ。悪くないよ、今は</t>
+          <t xml:space="preserve">……{name}さん、{stat}が頭打ちです。時間がかかりますね</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.named_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.near_cap[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -4518,19 +4518,19 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.named_positive[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.near_cap[1]</t>
         </is>
       </c>
       <c r="G158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、最近いい顔して練習に来るんだよなあ</t>
+          <t xml:space="preserve">……{name}さんの{stat}、もう天井が近いです</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.named_positive[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.near_cap[2]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -4545,19 +4545,19 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.named_positive[2]</t>
+          <t xml:space="preserve">artisan_seihitsu.near_cap[2]</t>
         </is>
       </c>
       <c r="G159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、乗ってるよ今。声かけたらもっと伸びるかもな</t>
+          <t xml:space="preserve">……{name}さん、{stat}は伸びしろが少ないです。守りに入る頃合いですね</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.named_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.far_from_cap[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -4572,19 +4572,19 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.named_negative[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.far_from_cap[1]</t>
         </is>
       </c>
       <c r="G160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、なんか元気ないんだよなあ最近。声かけといてやってくれよ</t>
+          <t xml:space="preserve">……{name}さんの{stat}、まだ奥があります</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.named_negative[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.far_from_cap[2]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -4599,19 +4599,19 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.named_negative[2]</t>
+          <t xml:space="preserve">artisan_seihitsu.far_from_cap[2]</t>
         </is>
       </c>
       <c r="G161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、飯の食いっぷりが落ちてる。心配だねえ</t>
+          <t xml:space="preserve">……{name}さん、{stat}はまだ伸びます。今は仕込み時ですね</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.named_neutral[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.strain_vague[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -4626,19 +4626,19 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.named_neutral[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.strain_vague[1]</t>
         </is>
       </c>
       <c r="G162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}は相変わらずマイペースだよ、あれはあれでいいんだよ</t>
+          <t xml:space="preserve">……どなたか、体を削っておられます。お名前は申しません</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.named_neutral[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.strain_vague[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -4653,19 +4653,19 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.named_neutral[2]</t>
+          <t xml:space="preserve">artisan_seihitsu.strain_vague[2]</t>
         </is>
       </c>
       <c r="G163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、特に変わりもなく元気にやってるよ</t>
+          <t xml:space="preserve">……無理を通しておられる方がいます。今は、保っています</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.stat_growing[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.strain_named[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -4680,19 +4680,19 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.stat_growing[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.strain_named[1]</t>
         </is>
       </c>
       <c r="G164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の{stat}、上がってきてるよ。あの子頑張ってるからなあ</t>
+          <t xml:space="preserve">……{name}さん、無理を通しておられますね。……今は、まだ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.stat_growing[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.strain_named[2]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -4707,19 +4707,19 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.stat_growing[2]</t>
+          <t xml:space="preserve">artisan_seihitsu.strain_named[2]</t>
         </is>
       </c>
       <c r="G165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、{stat}に手応え出てきたよ。見てて嬉しくなるね</t>
+          <t xml:space="preserve">……{name}さん、体に借りを作っておられます。返す日が参ります</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.stat_stagnant[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.strain_injured[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -4734,19 +4734,19 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.stat_stagnant[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.strain_injured[1]</t>
         </is>
       </c>
       <c r="G166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の{stat}、ちょっと足踏みしてるなあ。まあこういう時期もあるさ</t>
+          <t xml:space="preserve">……{name}さんのお怪我、軽いものです。……軽いうちは</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.stat_stagnant[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.artisan_seihitsu.strain_injured[2]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -4761,19 +4761,19 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.stat_stagnant[2]</t>
+          <t xml:space="preserve">artisan_seihitsu.strain_injured[2]</t>
         </is>
       </c>
       <c r="G167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、{stat}が伸びなくて焦ってるみたいだけど、気長にいこうや</t>
+          <t xml:space="preserve">……{name}さん、すぐ戻られます。ですが、残ります</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.near_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.vague[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -4788,19 +4788,19 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.near_cap[1]</t>
+          <t xml:space="preserve">mentor.vague[1]</t>
         </is>
       </c>
       <c r="G168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の{stat}、もうだいぶ頭打ち近いなあ。ここまで来たらたいしたもんだよ</t>
+          <t xml:space="preserve">誰かの表情が、最近柔らかくなってきましたよ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.near_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.vague[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -4815,19 +4815,19 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.near_cap[2]</t>
+          <t xml:space="preserve">mentor.vague[2]</t>
         </is>
       </c>
       <c r="G169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、{stat}はこれ以上は厳しいと思うよ。十分やったさ</t>
+          <t xml:space="preserve">あの子かな……まだ誰とは言えませんが、いい変化があります</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.far_from_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.vague[3]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -4842,19 +4842,19 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.far_from_cap[1]</t>
+          <t xml:space="preserve">mentor.vague[3]</t>
         </is>
       </c>
       <c r="G170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の{stat}、まだまだ伸びるよこれ。楽しみだねえ</t>
+          <t xml:space="preserve">練習場全体の空気が、少し温かくなった気がします</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.far_from_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.named_positive[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -4869,19 +4869,19 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.far_from_cap[2]</t>
+          <t xml:space="preserve">mentor.named_positive[1]</t>
         </is>
       </c>
       <c r="G171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、{stat}には余裕あるよ。今のうちにしっかり鍛えとこう</t>
+          <t xml:space="preserve">{name}さん、最近すごく前向きな顔をしていますよ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.vague[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.named_positive[2]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -4896,19 +4896,19 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.vague[1]</t>
+          <t xml:space="preserve">mentor.named_positive[2]</t>
         </is>
       </c>
       <c r="G172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰とは言わないけどね、目つきが変わった子がいるのよ</t>
+          <t xml:space="preserve">{name}さん、自分でも手応えを感じ始めているみたいです</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.vague[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.named_negative[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -4923,19 +4923,19 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.vague[2]</t>
+          <t xml:space="preserve">mentor.named_negative[1]</t>
         </is>
       </c>
       <c r="G173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんかいい空気なのよね、最近の練習場</t>
+          <t xml:space="preserve">{name}さん、少し元気がないかもしれません。気にかけてあげてください</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.vague[3]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.named_negative[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -4950,19 +4950,19 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.vague[3]</t>
+          <t xml:space="preserve">mentor.named_negative[2]</t>
         </is>
       </c>
       <c r="G174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">飯の食い方見てりゃわかるものよ。悪くないわ、今は</t>
+          <t xml:space="preserve">{name}さん、練習中に何か考え込んでいる時間が増えました</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.named_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.named_neutral[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -4977,19 +4977,19 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.named_positive[1]</t>
+          <t xml:space="preserve">mentor.named_neutral[1]</t>
         </is>
       </c>
       <c r="G175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、最近いい顔して練習に来るのよ</t>
+          <t xml:space="preserve">{name}さん、いつものペースでやっていますよ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.named_positive[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.named_neutral[2]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5004,19 +5004,19 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.named_positive[2]</t>
+          <t xml:space="preserve">mentor.named_neutral[2]</t>
         </is>
       </c>
       <c r="G176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、乗ってるわね今。声かけたらもっと伸びるかもよ</t>
+          <t xml:space="preserve">{name}さん、落ち着いて過ごせているみたいです</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.named_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.stat_growing[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5031,19 +5031,19 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.named_negative[1]</t>
+          <t xml:space="preserve">mentor.stat_growing[1]</t>
         </is>
       </c>
       <c r="G177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、なんか元気ないのよね最近。声かけてあげて</t>
+          <t xml:space="preserve">{name}さんの{stat}、着実に伸びてきていますよ。本人も気づいているはずです</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.named_negative[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.stat_growing[2]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5058,19 +5058,19 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.named_negative[2]</t>
+          <t xml:space="preserve">mentor.stat_growing[2]</t>
         </is>
       </c>
       <c r="G178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、飯の食いっぷりが落ちてるわ。心配ね</t>
+          <t xml:space="preserve">{name}さん、{stat}が良くなってきています。焦らず続けましょう</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.named_neutral[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5085,19 +5085,19 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.named_neutral[1]</t>
+          <t xml:space="preserve">mentor.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="G179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}は相変わらずマイペースね、あれはあれでいいのよ</t>
+          <t xml:space="preserve">{name}さんの{stat}、少し足踏みしていますね。でも悪いことではありませんよ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.named_neutral[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5112,19 +5112,19 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.named_neutral[2]</t>
+          <t xml:space="preserve">mentor.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="G180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、特に変わりもなく元気にやってるわよ</t>
+          <t xml:space="preserve">{name}さん、{stat}が伸び悩んでいます。本人も気づいているみたいです</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.stat_growing[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.near_cap[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5139,19 +5139,19 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.stat_growing[1]</t>
+          <t xml:space="preserve">mentor.near_cap[1]</t>
         </is>
       </c>
       <c r="G181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の{stat}、上がってきてるわよ。あの子頑張ってるものね</t>
+          <t xml:space="preserve">{name}さんの{stat}、もう十分に高いところまで来ていますよ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.stat_growing[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.near_cap[2]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -5166,19 +5166,19 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.stat_growing[2]</t>
+          <t xml:space="preserve">mentor.near_cap[2]</t>
         </is>
       </c>
       <c r="G182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、{stat}に手応え出てきたわ。見てて嬉しくなるわね</t>
+          <t xml:space="preserve">{name}さん、{stat}はこの先はゆっくりになると思います。それも成熟の証です</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.stat_stagnant[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.far_from_cap[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -5193,19 +5193,19 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.stat_stagnant[1]</t>
+          <t xml:space="preserve">mentor.far_from_cap[1]</t>
         </is>
       </c>
       <c r="G183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の{stat}、ちょっと足踏みしてるわね。まあこういう時期もあるわ</t>
+          <t xml:space="preserve">{name}さんの{stat}、まだまだこれからですよ。楽しみです</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.stat_stagnant[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.far_from_cap[2]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -5220,19 +5220,19 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.stat_stagnant[2]</t>
+          <t xml:space="preserve">mentor.far_from_cap[2]</t>
         </is>
       </c>
       <c r="G184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、{stat}が伸びなくて焦ってるみたいだけど、気長にいきましょ</t>
+          <t xml:space="preserve">{name}さん、{stat}には十分な余地が残っています。焦らず育てましょう</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.near_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.strain_vague[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -5247,19 +5247,19 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.near_cap[1]</t>
+          <t xml:space="preserve">mentor.strain_vague[1]</t>
         </is>
       </c>
       <c r="G185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の{stat}、もうだいぶ頭打ち近いわね。ここまで来たらたいしたものよ</t>
+          <t xml:space="preserve">ひとり、少し無理をしている子がいます。……今は元気なんですけどね</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.near_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.strain_vague[2]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -5274,19 +5274,19 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.near_cap[2]</t>
+          <t xml:space="preserve">mentor.strain_vague[2]</t>
         </is>
       </c>
       <c r="G186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、{stat}はこれ以上は厳しいと思うわ。十分やったわよ</t>
+          <t xml:space="preserve">頑張りすぎている子がいる気がします。今はまだ、平気そうにしていますが</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.far_from_cap[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.strain_named[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -5301,19 +5301,19 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.far_from_cap[1]</t>
+          <t xml:space="preserve">mentor.strain_named[1]</t>
         </is>
       </c>
       <c r="G187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の{stat}、まだまだ伸びるわよこれ。楽しみね</t>
+          <t xml:space="preserve">{name}さん、よく頑張っています。……頑張りすぎていないといいのですが</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.far_from_cap[2]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.strain_named[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -5328,19 +5328,19 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.far_from_cap[2]</t>
+          <t xml:space="preserve">mentor.strain_named[2]</t>
         </is>
       </c>
       <c r="G188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、{stat}には余裕あるわ。今のうちにしっかり鍛えときましょ</t>
+          <t xml:space="preserve">{name}さん、体はまだ持ちこたえています。……今のうちに、休ませてあげたいところです</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.C_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.strain_injured[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -5350,24 +5350,24 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi.C_positive[1]</t>
+          <t xml:space="preserve">mentor.strain_injured[1]</t>
         </is>
       </c>
       <c r="G189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">多分、素直に受け入れるとらん……いや、受け入れるだろう。潮時は本人が一番わかる</t>
+          <t xml:space="preserve">{name}さんの怪我、軽いものですけれど。……これが先々の問題にならなければいいのですが</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.C_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.mentor.strain_injured[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -5377,24 +5377,24 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi.C_negative[1]</t>
+          <t xml:space="preserve">mentor.strain_injured[2]</t>
         </is>
       </c>
       <c r="G190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ早いかもしれん。目にまだ光が残っとる</t>
+          <t xml:space="preserve">{name}さん、すぐ戻れます。……ただ、こういうものは積み重なりますからね</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.B_high[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.vague[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -5404,24 +5404,24 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi.B_high[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.vague[1]</t>
         </is>
       </c>
       <c r="G191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本人はもう覚悟を決めとる目だ。通るだろう</t>
+          <t xml:space="preserve">誰とは言わないけどよ、目つきが変わった奴がいるんだよ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.B_maybe[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.vague[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi.B_maybe[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.vague[2]</t>
         </is>
       </c>
       <c r="G192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、五分と見とる。伝え方一つで転ぶぞ</t>
+          <t xml:space="preserve">なんかいい空気なんだよなあ、最近の練習場</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.B_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.vague[3]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -5458,24 +5458,24 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi.B_hard[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.vague[3]</t>
         </is>
       </c>
       <c r="G193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ闘志が消えとらん。断られる覚悟はしておけ</t>
+          <t xml:space="preserve">飯の食い方見てりゃわかるもんさ。悪くないよ、今は</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.A_sure[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.named_positive[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -5485,24 +5485,24 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi.A_sure[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.named_positive[1]</t>
         </is>
       </c>
       <c r="G194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">間違いない。あれはもう己の中で決着をつけとる</t>
+          <t xml:space="preserve">{name}、最近いい顔して練習に来るんだよなあ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.A_likely[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.named_positive[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -5512,24 +5512,24 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi.A_likely[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.named_positive[2]</t>
         </is>
       </c>
       <c r="G195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">多分、通る。練習終わりの背中に、覚悟が見える</t>
+          <t xml:space="preserve">{name}、乗ってるよ今。声かけたらもっと伸びるかもな</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.A_iffy[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.named_negative[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -5539,24 +5539,24 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi.A_iffy[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.named_negative[1]</t>
         </is>
       </c>
       <c r="G196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">読めん。あれの中でも、まだ答えが出とらん</t>
+          <t xml:space="preserve">{name}、なんか元気ないんだよなあ最近。声かけといてやってくれよ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.A_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.named_negative[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -5566,24 +5566,24 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi.A_hard[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.named_negative[2]</t>
         </is>
       </c>
       <c r="G197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やめておけ。あの目はまだ、辞める目じゃない</t>
+          <t xml:space="preserve">{name}、飯の食いっぷりが落ちてる。心配だねえ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.C_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.named_neutral[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -5593,24 +5593,24 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.C_positive[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.named_neutral[1]</t>
         </is>
       </c>
       <c r="G198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">多分、受け入れる。潮時は本人が一番わかっている</t>
+          <t xml:space="preserve">{name}は相変わらずマイペースだよ、あれはあれでいいんだよ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.C_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.named_neutral[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -5620,24 +5620,24 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.C_negative[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.named_neutral[2]</t>
         </is>
       </c>
       <c r="G199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ早いかもしれない。目にまだ光が残っている</t>
+          <t xml:space="preserve">{name}、特に変わりもなく元気にやってるよ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.B_high[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.stat_growing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -5647,24 +5647,24 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.B_high[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.stat_growing[1]</t>
         </is>
       </c>
       <c r="G200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本人はもう覚悟を決めた目をしている。通るはず</t>
+          <t xml:space="preserve">{name}の{stat}、上がってきてるよ。あの子頑張ってるからなあ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.B_maybe[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.stat_growing[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -5674,24 +5674,24 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.B_maybe[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.stat_growing[2]</t>
         </is>
       </c>
       <c r="G201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、五分と見ている。伝え方ひとつで転ぶ</t>
+          <t xml:space="preserve">{name}、{stat}に手応え出てきたよ。見てて嬉しくなるね</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.B_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -5701,24 +5701,24 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.B_hard[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="G202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ闘志が消えていない。断られる覚悟はしておくべき</t>
+          <t xml:space="preserve">{name}の{stat}、ちょっと足踏みしてるなあ。まあこういう時期もあるさ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.A_sure[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -5728,24 +5728,24 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.A_sure[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="G203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">間違いない。もう己の中で決着をつけている</t>
+          <t xml:space="preserve">{name}、{stat}が伸びなくて焦ってるみたいだけど、気長にいこうや</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.A_likely[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.near_cap[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -5755,24 +5755,24 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.A_likely[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.near_cap[1]</t>
         </is>
       </c>
       <c r="G204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">多分、通る。練習終わりの背中に、覚悟が見える</t>
+          <t xml:space="preserve">{name}の{stat}、もうだいぶ頭打ち近いなあ。ここまで来たらたいしたもんだよ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.A_iffy[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.near_cap[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -5782,24 +5782,24 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.A_iffy[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.near_cap[2]</t>
         </is>
       </c>
       <c r="G205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">読めない。まだ本人の中でも答えが出ていない</t>
+          <t xml:space="preserve">{name}、{stat}はこれ以上は厳しいと思うよ。十分やったさ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.A_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.far_from_cap[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -5809,24 +5809,24 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho.A_hard[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.far_from_cap[1]</t>
         </is>
       </c>
       <c r="G206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やめておくべき。あの目はまだ、辞める目ではない</t>
+          <t xml:space="preserve">{name}の{stat}、まだまだ伸びるよこれ。楽しみだねえ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.C_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.far_from_cap[2]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -5836,24 +5836,24 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.C_positive[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.far_from_cap[2]</t>
         </is>
       </c>
       <c r="G207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本人の様子を見る限り、受容の可能性は高いと見立てています</t>
+          <t xml:space="preserve">{name}、{stat}には余裕あるよ。今のうちにしっかり鍛えとこう</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.C_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.strain_vague[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -5863,24 +5863,24 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.C_negative[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.strain_vague[1]</t>
         </is>
       </c>
       <c r="G208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">現時点のデータからは、時期尚早である可能性が高いと見ています</t>
+          <t xml:space="preserve">誰とは言わねえけどよ、ちょっと無理してる奴がいるんだよなあ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.B_high[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.strain_vague[2]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -5890,24 +5890,24 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.B_high[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.strain_vague[2]</t>
         </is>
       </c>
       <c r="G209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習中の言動から見て、本人の受容度はかなり高いと判断できます</t>
+          <t xml:space="preserve">無茶してる奴がいるんだよ。今は平気な顔してるけどなあ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.B_maybe[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.strain_named[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -5917,24 +5917,24 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.B_maybe[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.strain_named[1]</t>
         </is>
       </c>
       <c r="G210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直なところ、受容と拒否は拮抗しています。判断材料が足りません</t>
+          <t xml:space="preserve">{name}、よく頑張ってるよ。……頑張りすぎてなきゃいいんだけどなあ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.B_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.strain_named[2]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -5944,24 +5944,24 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.B_hard[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.strain_named[2]</t>
         </is>
       </c>
       <c r="G211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">闘争心の指標がまだ高水準です。拒否の可能性が高いと見ています</t>
+          <t xml:space="preserve">{name}、今は体が持ってるよ。持ってるうちが花なんだよなあ、ああいうのは</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.A_sure[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.strain_injured[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -5971,24 +5971,24 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.A_sure[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.strain_injured[1]</t>
         </is>
       </c>
       <c r="G212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">複数の兆候が揃っています。間違いなく受容すると判断します</t>
+          <t xml:space="preserve">{name}のあの怪我、大したことねえよ。……大したことにならなきゃいいけどなあ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.A_likely[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_oyaji.strain_injured[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -5998,24 +5998,24 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.A_likely[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.strain_injured[2]</t>
         </is>
       </c>
       <c r="G213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">確度は高いと見ます。行動データの傾向が一致しています</t>
+          <t xml:space="preserve">{name}、すぐ戻るさ。……まあ、こういうのは積もるんだけどな</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.A_iffy[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.vague[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -6025,24 +6025,24 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.A_iffy[1]</t>
+          <t xml:space="preserve">bigheart_anego.vague[1]</t>
         </is>
       </c>
       <c r="G214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">データが矛盾しています。正直、予測は困難です</t>
+          <t xml:space="preserve">誰とは言わないけどね、目つきが変わった子がいるのよ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.A_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.vague[2]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -6052,24 +6052,24 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist.A_hard[1]</t>
+          <t xml:space="preserve">bigheart_anego.vague[2]</t>
         </is>
       </c>
       <c r="G215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">断言します。現時点での提案は逆効果になる公算が大きいです</t>
+          <t xml:space="preserve">なんかいい空気なのよね、最近の練習場</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.C_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.vague[3]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -6079,24 +6079,24 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.C_positive[1]</t>
+          <t xml:space="preserve">bigheart_anego.vague[3]</t>
         </is>
       </c>
       <c r="G216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……たぶん、大丈夫だろう</t>
+          <t xml:space="preserve">飯の食い方見てりゃわかるものよ。悪くないわ、今は</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.C_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.named_positive[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -6106,24 +6106,24 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.C_negative[1]</t>
+          <t xml:space="preserve">bigheart_anego.named_positive[1]</t>
         </is>
       </c>
       <c r="G217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……早い。まだ、やる気だ</t>
+          <t xml:space="preserve">{name}、最近いい顔して練習に来るのよ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.B_high[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.named_positive[2]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -6133,24 +6133,24 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.B_high[1]</t>
+          <t xml:space="preserve">bigheart_anego.named_positive[2]</t>
         </is>
       </c>
       <c r="G218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの目は、もう決めとる</t>
+          <t xml:space="preserve">{name}、乗ってるわね今。声かけたらもっと伸びるかもよ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.B_maybe[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.named_negative[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -6160,24 +6160,24 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.B_maybe[1]</t>
+          <t xml:space="preserve">bigheart_anego.named_negative[1]</t>
         </is>
       </c>
       <c r="G219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……半々だ。読めん</t>
+          <t xml:space="preserve">{name}、なんか元気ないのよね最近。声かけてあげて</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.B_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.named_negative[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -6187,24 +6187,24 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.B_hard[1]</t>
+          <t xml:space="preserve">bigheart_anego.named_negative[2]</t>
         </is>
       </c>
       <c r="G220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……目が、死んどらん</t>
+          <t xml:space="preserve">{name}、飯の食いっぷりが落ちてるわ。心配ね</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.A_sure[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.named_neutral[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -6214,24 +6214,24 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.A_sure[1]</t>
+          <t xml:space="preserve">bigheart_anego.named_neutral[1]</t>
         </is>
       </c>
       <c r="G221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……間違いない。もう、決めとる</t>
+          <t xml:space="preserve">{name}は相変わらずマイペースね、あれはあれでいいのよ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.A_likely[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.named_neutral[2]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -6241,24 +6241,24 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.A_likely[1]</t>
+          <t xml:space="preserve">bigheart_anego.named_neutral[2]</t>
         </is>
       </c>
       <c r="G222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……たぶん、いい返事が来る</t>
+          <t xml:space="preserve">{name}、特に変わりもなく元気にやってるわよ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.A_iffy[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.stat_growing[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -6268,24 +6268,24 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.A_iffy[1]</t>
+          <t xml:space="preserve">bigheart_anego.stat_growing[1]</t>
         </is>
       </c>
       <c r="G223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……読めん。闘志と、体が食い違っとる</t>
+          <t xml:space="preserve">{name}の{stat}、上がってきてるわよ。あの子頑張ってるものね</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.A_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.stat_growing[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -6295,24 +6295,24 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu.A_hard[1]</t>
+          <t xml:space="preserve">bigheart_anego.stat_growing[2]</t>
         </is>
       </c>
       <c r="G224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よせ。まだ、その時じゃない</t>
+          <t xml:space="preserve">{name}、{stat}に手応え出てきたわ。見てて嬉しくなるわね</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.C_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -6322,24 +6322,24 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.C_positive[1]</t>
+          <t xml:space="preserve">bigheart_anego.stat_stagnant[1]</t>
         </is>
       </c>
       <c r="G225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……たぶん、大丈夫だと思います</t>
+          <t xml:space="preserve">{name}の{stat}、ちょっと足踏みしてるわね。まあこういう時期もあるわ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.C_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -6349,24 +6349,24 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.C_negative[1]</t>
+          <t xml:space="preserve">bigheart_anego.stat_stagnant[2]</t>
         </is>
       </c>
       <c r="G226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……早いと思います。まだ、やる気ですから</t>
+          <t xml:space="preserve">{name}、{stat}が伸びなくて焦ってるみたいだけど、気長にいきましょ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.B_high[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.near_cap[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.B_high[1]</t>
+          <t xml:space="preserve">bigheart_anego.near_cap[1]</t>
         </is>
       </c>
       <c r="G227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの目は、もう決めていらっしゃいます</t>
+          <t xml:space="preserve">{name}の{stat}、もうだいぶ頭打ち近いわね。ここまで来たらたいしたものよ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.B_maybe[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.near_cap[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -6403,24 +6403,24 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.B_maybe[1]</t>
+          <t xml:space="preserve">bigheart_anego.near_cap[2]</t>
         </is>
       </c>
       <c r="G228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……半々です。読めません</t>
+          <t xml:space="preserve">{name}、{stat}はこれ以上は厳しいと思うわ。十分やったわよ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.B_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.far_from_cap[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -6430,24 +6430,24 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.B_hard[1]</t>
+          <t xml:space="preserve">bigheart_anego.far_from_cap[1]</t>
         </is>
       </c>
       <c r="G229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……目が、死んでいらっしゃいません</t>
+          <t xml:space="preserve">{name}の{stat}、まだまだ伸びるわよこれ。楽しみね</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.A_sure[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.far_from_cap[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -6457,24 +6457,24 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.A_sure[1]</t>
+          <t xml:space="preserve">bigheart_anego.far_from_cap[2]</t>
         </is>
       </c>
       <c r="G230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……間違いありません。もう、決めていらっしゃいます</t>
+          <t xml:space="preserve">{name}、{stat}には余裕あるわ。今のうちにしっかり鍛えときましょ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.A_likely[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.strain_vague[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -6484,24 +6484,24 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.A_likely[1]</t>
+          <t xml:space="preserve">bigheart_anego.strain_vague[1]</t>
         </is>
       </c>
       <c r="G231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……たぶん、いい返事が来ると思います</t>
+          <t xml:space="preserve">誰とは言わないけどね、ちょっと無理してる子がいるのよ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.A_iffy[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.strain_vague[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -6511,24 +6511,24 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.A_iffy[1]</t>
+          <t xml:space="preserve">bigheart_anego.strain_vague[2]</t>
         </is>
       </c>
       <c r="G232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……読めません。闘志と、お身体が食い違っています</t>
+          <t xml:space="preserve">無茶してる子がいるわ。今は平気な顔してるけどね</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.A_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.strain_named[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -6538,24 +6538,24 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu.A_hard[1]</t>
+          <t xml:space="preserve">bigheart_anego.strain_named[1]</t>
         </is>
       </c>
       <c r="G233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……おやめください。まだ、その時ではありません</t>
+          <t xml:space="preserve">{name}、よく頑張ってるわ。……頑張りすぎてなきゃいいんだけどね</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.C_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.strain_named[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -6565,24 +6565,24 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.C_positive[1]</t>
+          <t xml:space="preserve">bigheart_anego.strain_named[2]</t>
         </is>
       </c>
       <c r="G234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本人もそろそろかな、という空気を出していますよ</t>
+          <t xml:space="preserve">{name}、今は体が持ってるわ。持ってるうちが花なのよ、ああいうのは</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.C_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.strain_injured[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -6592,24 +6592,24 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.C_negative[1]</t>
+          <t xml:space="preserve">bigheart_anego.strain_injured[1]</t>
         </is>
       </c>
       <c r="G235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本人はまだやる気みたいですよ。難しいかもしれません</t>
+          <t xml:space="preserve">{name}のあの怪我、大したことないわ。……大したことにならなきゃいいけどね</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.B_high[1]</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES.bigheart_anego.strain_injured[2]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -6619,24 +6619,24 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_REPORT_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.B_high[1]</t>
+          <t xml:space="preserve">bigheart_anego.strain_injured[2]</t>
         </is>
       </c>
       <c r="G236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本人も覚悟しているようです。大丈夫だと思いますよ</t>
+          <t xml:space="preserve">{name}、すぐ戻るわよ。……まあ、こういうのは積もるんだけどね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.B_maybe[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.C_positive[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -6651,19 +6651,19 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.B_maybe[1]</t>
+          <t xml:space="preserve">sparta_roshi.C_positive[1]</t>
         </is>
       </c>
       <c r="G237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、気持ちは揺れていると思います。タイミング次第ですね</t>
+          <t xml:space="preserve">多分、素直に受け入れるとらん……いや、受け入れるだろう。潮時は本人が一番わかる</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.B_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.C_negative[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -6678,19 +6678,19 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.B_hard[1]</t>
+          <t xml:space="preserve">sparta_roshi.C_negative[1]</t>
         </is>
       </c>
       <c r="G238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ本人には闘志がありますね。断られる覚悟はしてください</t>
+          <t xml:space="preserve">まだ早いかもしれん。目にまだ光が残っとる</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.A_sure[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.B_high[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -6705,19 +6705,19 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.A_sure[1]</t>
+          <t xml:space="preserve">sparta_roshi.B_high[1]</t>
         </is>
       </c>
       <c r="G239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">間違いなく受け入れます。本人もそのつもりですよ</t>
+          <t xml:space="preserve">本人はもう覚悟を決めとる目だ。通るだろう</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.A_likely[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.B_maybe[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -6732,19 +6732,19 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.A_likely[1]</t>
+          <t xml:space="preserve">sparta_roshi.B_maybe[1]</t>
         </is>
       </c>
       <c r="G240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習後の表情を見ていると……受け入れると思います</t>
+          <t xml:space="preserve">正直、五分と見とる。伝え方一つで転ぶぞ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.A_iffy[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.B_hard[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -6759,19 +6759,19 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.A_iffy[1]</t>
+          <t xml:space="preserve">sparta_roshi.B_hard[1]</t>
         </is>
       </c>
       <c r="G241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直読めないです。本人の中でも揺れてる感じですね</t>
+          <t xml:space="preserve">まだ闘志が消えとらん。断られる覚悟はしておけ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.A_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.A_sure[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -6786,19 +6786,19 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor.A_hard[1]</t>
+          <t xml:space="preserve">sparta_roshi.A_sure[1]</t>
         </is>
       </c>
       <c r="G242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止めた方がいい。あの目はまだ引退する目じゃありませんよ</t>
+          <t xml:space="preserve">間違いない。あれはもう己の中で決着をつけとる</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.C_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.A_likely[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -6813,19 +6813,19 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.C_positive[1]</t>
+          <t xml:space="preserve">sparta_roshi.A_likely[1]</t>
         </is>
       </c>
       <c r="G243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子ならすんなり受け入れてくれると思うよ、多分な</t>
+          <t xml:space="preserve">多分、通る。練習終わりの背中に、覚悟が見える</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.C_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.A_iffy[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -6840,19 +6840,19 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.C_negative[1]</t>
+          <t xml:space="preserve">sparta_roshi.A_iffy[1]</t>
         </is>
       </c>
       <c r="G244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやまだ早いんじゃないかなあ。あの子まだやる気満々だよ</t>
+          <t xml:space="preserve">読めん。あれの中でも、まだ答えが出とらん</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.B_high[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_roshi.A_hard[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -6867,19 +6867,19 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.B_high[1]</t>
+          <t xml:space="preserve">sparta_roshi.A_hard[1]</t>
         </is>
       </c>
       <c r="G245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本人ももう腹くくってる顔してるよ。大丈夫だろうな</t>
+          <t xml:space="preserve">やめておけ。あの目はまだ、辞める目じゃない</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.B_maybe[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.C_positive[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -6894,19 +6894,19 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.B_maybe[1]</t>
+          <t xml:space="preserve">sparta_tosho.C_positive[1]</t>
         </is>
       </c>
       <c r="G246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直五分五分だなあ。あの子の中でも揺れてる感じだよ</t>
+          <t xml:space="preserve">多分、受け入れる。潮時は本人が一番わかっている</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.B_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.C_negative[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -6921,19 +6921,19 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.B_hard[1]</t>
+          <t xml:space="preserve">sparta_tosho.C_negative[1]</t>
         </is>
       </c>
       <c r="G247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだあいつ目が死んでないよ。断られる覚悟はしといた方がいい</t>
+          <t xml:space="preserve">まだ早いかもしれない。目にまだ光が残っている</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.A_sure[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.B_high[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -6948,19 +6948,19 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.A_sure[1]</t>
+          <t xml:space="preserve">sparta_tosho.B_high[1]</t>
         </is>
       </c>
       <c r="G248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">間違いないよ。あの子もう次の身の振り方まで考えてるからな</t>
+          <t xml:space="preserve">本人はもう覚悟を決めた目をしている。通るはず</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.A_likely[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.B_maybe[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -6975,19 +6975,19 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.A_likely[1]</t>
+          <t xml:space="preserve">sparta_tosho.B_maybe[1]</t>
         </is>
       </c>
       <c r="G249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">多分通るんじゃないかなあ。あの子薄々わかってる顔してるよ</t>
+          <t xml:space="preserve">正直、五分と見ている。伝え方ひとつで転ぶ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.A_iffy[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.B_hard[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -7002,19 +7002,19 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.A_iffy[1]</t>
+          <t xml:space="preserve">sparta_tosho.B_hard[1]</t>
         </is>
       </c>
       <c r="G250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">読めないんだよなあ、これが。闘志はあるけど体がついてこないみたいでさ</t>
+          <t xml:space="preserve">まだ闘志が消えていない。断られる覚悟はしておくべき</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.A_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.A_sure[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -7029,19 +7029,19 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji.A_hard[1]</t>
+          <t xml:space="preserve">sparta_tosho.A_sure[1]</t>
         </is>
       </c>
       <c r="G251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やめときな、今は。あの目はまだ辞める目じゃないよ、絶対に</t>
+          <t xml:space="preserve">間違いない。もう己の中で決着をつけている</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.C_positive[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.A_likely[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -7056,19 +7056,19 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.C_positive[1]</t>
+          <t xml:space="preserve">sparta_tosho.A_likely[1]</t>
         </is>
       </c>
       <c r="G252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子ならすんなり受け入れてくれると思うわ、多分ね</t>
+          <t xml:space="preserve">多分、通る。練習終わりの背中に、覚悟が見える</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.C_negative[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.A_iffy[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -7083,19 +7083,19 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.C_negative[1]</t>
+          <t xml:space="preserve">sparta_tosho.A_iffy[1]</t>
         </is>
       </c>
       <c r="G253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやまだ早いんじゃないかしら。あの子まだやる気満々よ</t>
+          <t xml:space="preserve">読めない。まだ本人の中でも答えが出ていない</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.B_high[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.sparta_tosho.A_hard[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -7110,19 +7110,19 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.B_high[1]</t>
+          <t xml:space="preserve">sparta_tosho.A_hard[1]</t>
         </is>
       </c>
       <c r="G254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本人ももう腹くくってる顔してるわよ。大丈夫だと思うわ</t>
+          <t xml:space="preserve">やめておくべき。あの目はまだ、辞める目ではない</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.B_maybe[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.C_positive[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -7137,19 +7137,19 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.B_maybe[1]</t>
+          <t xml:space="preserve">theorist.C_positive[1]</t>
         </is>
       </c>
       <c r="G255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直五分五分ね。あの子の中でも揺れてる感じよ</t>
+          <t xml:space="preserve">本人の様子を見る限り、受容の可能性は高いと見立てています</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.B_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.C_negative[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -7164,19 +7164,19 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.B_hard[1]</t>
+          <t xml:space="preserve">theorist.C_negative[1]</t>
         </is>
       </c>
       <c r="G256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだあの子目が死んでないわよ。断られる覚悟はしといた方がいいわ</t>
+          <t xml:space="preserve">現時点のデータからは、時期尚早である可能性が高いと見ています</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.A_sure[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.B_high[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -7191,19 +7191,19 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.A_sure[1]</t>
+          <t xml:space="preserve">theorist.B_high[1]</t>
         </is>
       </c>
       <c r="G257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">間違いないわ。あの子もう次の身の振り方まで考えてるもの</t>
+          <t xml:space="preserve">練習中の言動から見て、本人の受容度はかなり高いと判断できます</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.A_likely[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.B_maybe[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -7218,19 +7218,19 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.A_likely[1]</t>
+          <t xml:space="preserve">theorist.B_maybe[1]</t>
         </is>
       </c>
       <c r="G258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">多分通るんじゃないかしら。あの子薄々わかってる顔してるわ</t>
+          <t xml:space="preserve">正直なところ、受容と拒否は拮抗しています。判断材料が足りません</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.A_iffy[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.B_hard[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -7245,19 +7245,19 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.A_iffy[1]</t>
+          <t xml:space="preserve">theorist.B_hard[1]</t>
         </is>
       </c>
       <c r="G259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">読めないのよねえ、これが。闘志はあるけど体がついてこないみたいでね</t>
+          <t xml:space="preserve">闘争心の指標がまだ高水準です。拒否の可能性が高いと見ています</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.A_hard[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.A_sure[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -7272,19 +7272,19 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego.A_hard[1]</t>
+          <t xml:space="preserve">theorist.A_sure[1]</t>
         </is>
       </c>
       <c r="G260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やめときなさい、今は。あの目はまだ辞める目じゃないわよ、絶対に</t>
+          <t xml:space="preserve">複数の兆候が揃っています。間違いなく受容すると判断します</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.sparta_roshi[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.A_likely[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -7294,24 +7294,24 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi[1]</t>
+          <t xml:space="preserve">theorist.A_likely[1]</t>
         </is>
       </c>
       <c r="G261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「わしを呼んだか。……いいだろう、鍛え直してやる」</t>
+          <t xml:space="preserve">確度は高いと見ます。行動データの傾向が一致しています</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.sparta_roshi[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.A_iffy[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -7321,24 +7321,24 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi[2]</t>
+          <t xml:space="preserve">theorist.A_iffy[1]</t>
         </is>
       </c>
       <c r="G262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「甘い顔はせんぞ。それでもいいなら、任せてもらおう」</t>
+          <t xml:space="preserve">データが矛盾しています。正直、予測は困難です</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.sparta_tosho[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.theorist.A_hard[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -7348,24 +7348,24 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho[1]</t>
+          <t xml:space="preserve">theorist.A_hard[1]</t>
         </is>
       </c>
       <c r="G263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「呼んだか。ならば、鍛え直す」</t>
+          <t xml:space="preserve">断言します。現時点での提案は逆効果になる公算が大きいです</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.sparta_tosho[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.C_positive[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -7375,24 +7375,24 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.C_positive[1]</t>
         </is>
       </c>
       <c r="G264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「甘い顔はしない。それでも構わないなら、引き受ける」</t>
+          <t xml:space="preserve">……たぶん、大丈夫だろう</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.theorist[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.C_negative[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -7402,24 +7402,24 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.C_negative[1]</t>
         </is>
       </c>
       <c r="G265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「お招きいただき光栄です。データに基づいて、着実に成果を出しましょう」</t>
+          <t xml:space="preserve">……早い。まだ、やる気だ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.theorist[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.B_high[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -7429,24 +7429,24 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.B_high[1]</t>
         </is>
       </c>
       <c r="G266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「拝見しました、伸びしろのある選手が揃っていますね。楽しみです」</t>
+          <t xml:space="preserve">……あの目は、もう決めとる</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.artisan_bukotsu[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.B_maybe[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -7456,24 +7456,24 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.B_maybe[1]</t>
         </is>
       </c>
       <c r="G267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「……よろしく頼む」</t>
+          <t xml:space="preserve">……半々だ。読めん</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.artisan_bukotsu[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.B_hard[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -7483,24 +7483,24 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.B_hard[1]</t>
         </is>
       </c>
       <c r="G268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「……手は抜かん」</t>
+          <t xml:space="preserve">……目が、死んどらん</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.artisan_seihitsu[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.A_sure[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -7510,24 +7510,24 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.A_sure[1]</t>
         </is>
       </c>
       <c r="G269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「……よろしくお願いします」</t>
+          <t xml:space="preserve">……間違いない。もう、決めとる</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.artisan_seihitsu[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.A_likely[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -7537,24 +7537,24 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.A_likely[1]</t>
         </is>
       </c>
       <c r="G270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「……手は抜きません」</t>
+          <t xml:space="preserve">……たぶん、いい返事が来る</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.mentor[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.A_iffy[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -7564,24 +7564,24 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor[1]</t>
+          <t xml:space="preserve">artisan_bukotsu.A_iffy[1]</t>
         </is>
       </c>
       <c r="G271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「よろしくお願いします。まずは選手一人ひとりを、よく見ることから始めますね」</t>
+          <t xml:space="preserve">……読めん。闘志と、体が食い違っとる</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.mentor[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_bukotsu.A_hard[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -7591,24 +7591,24 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor[2]</t>
+          <t xml:space="preserve">artisan_bukotsu.A_hard[1]</t>
         </is>
       </c>
       <c r="G272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「お力になれるよう、じっくり向き合っていきます」</t>
+          <t xml:space="preserve">……よせ。まだ、その時じゃない</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.bigheart_oyaji[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.C_positive[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -7618,24 +7618,24 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.C_positive[1]</t>
         </is>
       </c>
       <c r="G273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「いやあ、呼んでくれて嬉しいねえ。よろしく頼むよ」</t>
+          <t xml:space="preserve">……たぶん、大丈夫だと思います</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.bigheart_oyaji[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.C_negative[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -7645,24 +7645,24 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji[2]</t>
+          <t xml:space="preserve">artisan_seihitsu.C_negative[1]</t>
         </is>
       </c>
       <c r="G274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「腕が鳴るなあ。みんなでいい汗かこうぜ」</t>
+          <t xml:space="preserve">……早いと思います。まだ、やる気ですから</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.bigheart_anego[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.B_high[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -7672,24 +7672,24 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.B_high[1]</t>
         </is>
       </c>
       <c r="G275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「あら、呼んでくれて嬉しいわ。よろしくね」</t>
+          <t xml:space="preserve">……あの目は、もう決めていらっしゃいます</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.bigheart_anego[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.B_maybe[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -7699,24 +7699,24 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego[2]</t>
+          <t xml:space="preserve">artisan_seihitsu.B_maybe[1]</t>
         </is>
       </c>
       <c r="G276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「腕が鳴るわねえ。みんなでいい汗かきましょ」</t>
+          <t xml:space="preserve">……半々です。読めません</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.sparta_roshi[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.B_hard[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -7726,24 +7726,24 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.B_hard[1]</t>
         </is>
       </c>
       <c r="G277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「そうか。……達者でな」</t>
+          <t xml:space="preserve">……目が、死んでいらっしゃいません</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.sparta_tosho[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.A_sure[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -7753,24 +7753,24 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.A_sure[1]</t>
         </is>
       </c>
       <c r="G278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「そうか。達者で」</t>
+          <t xml:space="preserve">……間違いありません。もう、決めていらっしゃいます</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.theorist[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.A_likely[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -7780,24 +7780,24 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.A_likely[1]</t>
         </is>
       </c>
       <c r="G279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「承知しました。短い間でしたが、良いデータが取れました」</t>
+          <t xml:space="preserve">……たぶん、いい返事が来ると思います</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.artisan_bukotsu[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.A_iffy[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -7807,24 +7807,24 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.A_iffy[1]</t>
         </is>
       </c>
       <c r="G280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「……そうか。世話になった」</t>
+          <t xml:space="preserve">……読めません。闘志と、お身体が食い違っています</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.artisan_seihitsu[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.artisan_seihitsu.A_hard[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -7834,24 +7834,24 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu[1]</t>
+          <t xml:space="preserve">artisan_seihitsu.A_hard[1]</t>
         </is>
       </c>
       <c r="G281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「……そうですか。お世話になりました」</t>
+          <t xml:space="preserve">……おやめください。まだ、その時ではありません</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.mentor[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.C_positive[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -7861,24 +7861,24 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor[1]</t>
+          <t xml:space="preserve">mentor.C_positive[1]</t>
         </is>
       </c>
       <c r="G282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「そうですか……。選手の皆さんによろしくお伝えください」</t>
+          <t xml:space="preserve">本人もそろそろかな、という空気を出していますよ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.bigheart_oyaji[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.C_negative[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -7888,24 +7888,24 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji[1]</t>
+          <t xml:space="preserve">mentor.C_negative[1]</t>
         </is>
       </c>
       <c r="G283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「そうかい……。世話になったなあ、ありがとよ」</t>
+          <t xml:space="preserve">本人はまだやる気みたいですよ。難しいかもしれません</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.bigheart_anego[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.B_high[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -7915,24 +7915,24 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego[1]</t>
+          <t xml:space="preserve">mentor.B_high[1]</t>
         </is>
       </c>
       <c r="G284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「そう……。お世話になったわね、ありがとう」</t>
+          <t xml:space="preserve">本人も覚悟しているようです。大丈夫だと思いますよ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.sparta_roshi[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.B_maybe[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -7942,24 +7942,24 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi[1]</t>
+          <t xml:space="preserve">mentor.B_maybe[1]</t>
         </is>
       </c>
       <c r="G285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「よくやった。……あそこまで追い込んだ甲斐があったわい」</t>
+          <t xml:space="preserve">正直、気持ちは揺れていると思います。タイミング次第ですね</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.sparta_roshi[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.B_hard[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -7969,24 +7969,24 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_roshi[2]</t>
+          <t xml:space="preserve">mentor.B_hard[1]</t>
         </is>
       </c>
       <c r="G286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「あれが、鍛えた者の顔だ。文句なしだ」</t>
+          <t xml:space="preserve">まだ本人には闘志がありますね。断られる覚悟はしてください</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.sparta_tosho[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.A_sure[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -7996,24 +7996,24 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho[1]</t>
+          <t xml:space="preserve">mentor.A_sure[1]</t>
         </is>
       </c>
       <c r="G287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「よくやった。追い込んだ甲斐があった」</t>
+          <t xml:space="preserve">間違いなく受け入れます。本人もそのつもりですよ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.sparta_tosho[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.A_likely[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -8023,24 +8023,24 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sparta_tosho[2]</t>
+          <t xml:space="preserve">mentor.A_likely[1]</t>
         </is>
       </c>
       <c r="G288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「あれが、鍛え抜いた者の顔。文句なし」</t>
+          <t xml:space="preserve">練習後の表情を見ていると……受け入れると思います</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.theorist[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.A_iffy[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -8050,24 +8050,24 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist[1]</t>
+          <t xml:space="preserve">mentor.A_iffy[1]</t>
         </is>
       </c>
       <c r="G289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「素晴らしい結果です。積み上げてきた数値が、そのまま結果に出ましたね」</t>
+          <t xml:space="preserve">正直読めないです。本人の中でも揺れてる感じですね</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.theorist[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.mentor.A_hard[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -8077,24 +8077,24 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">theorist[2]</t>
+          <t xml:space="preserve">mentor.A_hard[1]</t>
         </is>
       </c>
       <c r="G290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「あの大舞台での再現性は、本物の実力の証明です」</t>
+          <t xml:space="preserve">止めた方がいい。あの目はまだ引退する目じゃありませんよ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.artisan_bukotsu[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.C_positive[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -8104,24 +8104,24 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.C_positive[1]</t>
         </is>
       </c>
       <c r="G291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「……いい試合だった」</t>
+          <t xml:space="preserve">あの子ならすんなり受け入れてくれると思うよ、多分な</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.artisan_bukotsu[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.C_negative[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -8131,24 +8131,24 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_bukotsu[2]</t>
+          <t xml:space="preserve">bigheart_oyaji.C_negative[1]</t>
         </is>
       </c>
       <c r="G292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「……よく、やった」</t>
+          <t xml:space="preserve">いやまだ早いんじゃないかなあ。あの子まだやる気満々だよ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.artisan_seihitsu[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.B_high[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -8158,24 +8158,24 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.B_high[1]</t>
         </is>
       </c>
       <c r="G293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「……いい試合でした」</t>
+          <t xml:space="preserve">本人ももう腹くくってる顔してるよ。大丈夫だろうな</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.artisan_seihitsu[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.B_maybe[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -8185,24 +8185,24 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">artisan_seihitsu[2]</t>
+          <t xml:space="preserve">bigheart_oyaji.B_maybe[1]</t>
         </is>
       </c>
       <c r="G294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「……よく、やりましたね」</t>
+          <t xml:space="preserve">正直五分五分だなあ。あの子の中でも揺れてる感じだよ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.mentor[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.B_hard[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -8212,24 +8212,24 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.B_hard[1]</t>
         </is>
       </c>
       <c r="G295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「本人が積み重ねてきたものが、ちゃんと実を結びましたね。嬉しいです」</t>
+          <t xml:space="preserve">まだあいつ目が死んでないよ。断られる覚悟はしといた方がいい</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.mentor[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.A_sure[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -8239,24 +8239,24 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mentor[2]</t>
+          <t xml:space="preserve">bigheart_oyaji.A_sure[1]</t>
         </is>
       </c>
       <c r="G296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「見ていて、こちらまで胸が熱くなりました」</t>
+          <t xml:space="preserve">間違いないよ。あの子もう次の身の振り方まで考えてるからな</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.bigheart_oyaji[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.A_likely[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -8266,24 +8266,24 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.A_likely[1]</t>
         </is>
       </c>
       <c r="G297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「いやあ最高だったよ！あの舞台であれだけやれるとはなあ」</t>
+          <t xml:space="preserve">多分通るんじゃないかなあ。あの子薄々わかってる顔してるよ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.bigheart_oyaji[2]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.A_iffy[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -8293,24 +8293,24 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_oyaji[2]</t>
+          <t xml:space="preserve">bigheart_oyaji.A_iffy[1]</t>
         </is>
       </c>
       <c r="G298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「見てて泣きそうになったよ。ほんとよく頑張ったなあ」</t>
+          <t xml:space="preserve">読めないんだよなあ、これが。闘志はあるけど体がついてこないみたいでさ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.bigheart_anego[1]</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_oyaji.A_hard[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -8320,49 +8320,1345 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigheart_anego[1]</t>
+          <t xml:space="preserve">bigheart_oyaji.A_hard[1]</t>
         </is>
       </c>
       <c r="G299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「もう最高だったわよ！あの舞台であれだけやれるなんてね」</t>
+          <t xml:space="preserve">やめときな、今は。あの目はまだ辞める目じゃないよ、絶対に</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.C_positive[1]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_anego.C_positive[1]</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの子ならすんなり受け入れてくれると思うわ、多分ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.C_negative[1]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_anego.C_negative[1]</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いやまだ早いんじゃないかしら。あの子まだやる気満々よ</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.B_high[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_anego.B_high[1]</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">本人ももう腹くくってる顔してるわよ。大丈夫だと思うわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.B_maybe[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_anego.B_maybe[1]</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">正直五分五分ね。あの子の中でも揺れてる感じよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.B_hard[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_anego.B_hard[1]</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだあの子目が死んでないわよ。断られる覚悟はしといた方がいいわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.A_sure[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_anego.A_sure[1]</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">間違いないわ。あの子もう次の身の振り方まで考えてるもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.A_likely[1]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_anego.A_likely[1]</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">多分通るんじゃないかしら。あの子薄々わかってる顔してるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.A_iffy[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_anego.A_iffy[1]</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">読めないのよねえ、これが。闘志はあるけど体がついてこないみたいでね</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES.bigheart_anego.A_hard[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_RETIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_anego.A_hard[1]</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やめときなさい、今は。あの目はまだ辞める目じゃないわよ、絶対に</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.sparta_roshi[1]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sparta_roshi[1]</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「わしを呼んだか。……いいだろう、鍛え直してやる」</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.sparta_roshi[2]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sparta_roshi[2]</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「甘い顔はせんぞ。それでもいいなら、任せてもらおう」</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.sparta_tosho[1]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sparta_tosho[1]</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「呼んだか。ならば、鍛え直す」</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.sparta_tosho[2]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sparta_tosho[2]</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「甘い顔はしない。それでも構わないなら、引き受ける」</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.theorist[1]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">theorist[1]</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「お招きいただき光栄です。データに基づいて、着実に成果を出しましょう」</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.theorist[2]</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">theorist[2]</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「拝見しました、伸びしろのある選手が揃っていますね。楽しみです」</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.artisan_bukotsu[1]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">artisan_bukotsu[1]</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「……よろしく頼む」</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.artisan_bukotsu[2]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">artisan_bukotsu[2]</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「……手は抜かん」</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.artisan_seihitsu[1]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">artisan_seihitsu[1]</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「……よろしくお願いします」</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.artisan_seihitsu[2]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">artisan_seihitsu[2]</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「……手は抜きません」</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.mentor[1]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">mentor[1]</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「よろしくお願いします。まずは選手一人ひとりを、よく見ることから始めますね」</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.mentor[2]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">mentor[2]</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「お力になれるよう、じっくり向き合っていきます」</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.bigheart_oyaji[1]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_oyaji[1]</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「いやあ、呼んでくれて嬉しいねえ。よろしく頼むよ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.bigheart_oyaji[2]</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_oyaji[2]</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「腕が鳴るなあ。みんなでいい汗かこうぜ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.bigheart_anego[1]</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_anego[1]</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「あら、呼んでくれて嬉しいわ。よろしくね」</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="40" customHeight="1">
+      <c r="A324" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES.bigheart_anego[2]</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_anego[2]</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「腕が鳴るわねえ。みんなでいい汗かきましょ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.sparta_roshi[1]</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sparta_roshi[1]</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「そうか。……達者でな」</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="40" customHeight="1">
+      <c r="A326" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.sparta_tosho[1]</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sparta_tosho[1]</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「そうか。達者で」</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="40" customHeight="1">
+      <c r="A327" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.theorist[1]</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">theorist[1]</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「承知しました。短い間でしたが、良いデータが取れました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="40" customHeight="1">
+      <c r="A328" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.artisan_bukotsu[1]</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">artisan_bukotsu[1]</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「……そうか。世話になった」</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="40" customHeight="1">
+      <c r="A329" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.artisan_seihitsu[1]</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">artisan_seihitsu[1]</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「……そうですか。お世話になりました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="40" customHeight="1">
+      <c r="A330" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.mentor[1]</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">mentor[1]</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「そうですか……。選手の皆さんによろしくお伝えください」</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="40" customHeight="1">
+      <c r="A331" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.bigheart_oyaji[1]</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_oyaji[1]</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「そうかい……。世話になったなあ、ありがとよ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="40" customHeight="1">
+      <c r="A332" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES.bigheart_anego[1]</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_anego[1]</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「そう……。お世話になったわね、ありがとう」</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="40" customHeight="1">
+      <c r="A333" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.sparta_roshi[1]</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sparta_roshi[1]</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「よくやった。……あそこまで追い込んだ甲斐があったわい」</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="40" customHeight="1">
+      <c r="A334" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.sparta_roshi[2]</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sparta_roshi[2]</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「あれが、鍛えた者の顔だ。文句なしだ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="40" customHeight="1">
+      <c r="A335" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.sparta_tosho[1]</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sparta_tosho[1]</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「よくやった。追い込んだ甲斐があった」</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="40" customHeight="1">
+      <c r="A336" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.sparta_tosho[2]</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sparta_tosho[2]</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「あれが、鍛え抜いた者の顔。文句なし」</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="40" customHeight="1">
+      <c r="A337" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.theorist[1]</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">theorist[1]</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「素晴らしい結果です。積み上げてきた数値が、そのまま結果に出ましたね」</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="40" customHeight="1">
+      <c r="A338" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.theorist[2]</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">theorist[2]</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「あの大舞台での再現性は、本物の実力の証明です」</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="40" customHeight="1">
+      <c r="A339" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.artisan_bukotsu[1]</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">artisan_bukotsu[1]</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「……いい試合だった」</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="40" customHeight="1">
+      <c r="A340" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.artisan_bukotsu[2]</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">artisan_bukotsu[2]</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「……よく、やった」</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="40" customHeight="1">
+      <c r="A341" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.artisan_seihitsu[1]</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">artisan_seihitsu[1]</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「……いい試合でした」</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="40" customHeight="1">
+      <c r="A342" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.artisan_seihitsu[2]</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">artisan_seihitsu[2]</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「……よく、やりましたね」</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="40" customHeight="1">
+      <c r="A343" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.mentor[1]</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">mentor[1]</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「本人が積み重ねてきたものが、ちゃんと実を結びましたね。嬉しいです」</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="40" customHeight="1">
+      <c r="A344" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.mentor[2]</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">mentor[2]</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「見ていて、こちらまで胸が熱くなりました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="40" customHeight="1">
+      <c r="A345" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.bigheart_oyaji[1]</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_oyaji[1]</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「いやあ最高だったよ！あの舞台であれだけやれるとはなあ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="40" customHeight="1">
+      <c r="A346" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.bigheart_oyaji[2]</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_oyaji[2]</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「見てて泣きそうになったよ。ほんとよく頑張ったなあ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="40" customHeight="1">
+      <c r="A347" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.bigheart_anego[1]</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bigheart_anego[1]</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「もう最高だったわよ！あの舞台であれだけやれるなんてね」</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="40" customHeight="1">
+      <c r="A348" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">COACH_VOICE_PRAISE_LINES.bigheart_anego[2]</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/coach-lines.js</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr" s="2">
+      <c r="B348" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/coach-lines.js</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">COACH_VOICE_PRAISE_LINES</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr" s="12">
+      <c r="D348" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bigheart_anego[2]</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr" s="3">
+      <c r="G348" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「見てて泣きそうになったわ。ほんとよく頑張ったわね」</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I300"/>
+  <autoFilter ref="A1:I348"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/コーチ/コーチボイス.xlsx
+++ b/セリフ編集/コーチ/コーチボイス.xlsx
@@ -1336,7 +1336,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIGHTER_INVITE_GRAD_LINES.normal</t>
+          <t xml:space="preserve">FIGHTER_INVITE_GRAD_LINES.standard</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G42" t="inlineStr" s="3">
